--- a/data/semantic_categories_and_concepts.xlsx
+++ b/data/semantic_categories_and_concepts.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249E9438-3F59-46D0-88C6-C0A902E66877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A41755-0473-4FD5-BD73-F333D57F41D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>style</t>
   </si>
   <si>
-    <t>breath</t>
-  </si>
-  <si>
     <t>depth</t>
   </si>
   <si>
@@ -212,6 +209,9 @@
   </si>
   <si>
     <t>Pointillism</t>
+  </si>
+  <si>
+    <t>breadth</t>
   </si>
 </sst>
 </file>
@@ -687,106 +687,106 @@
   <sheetData>
     <row r="1" spans="1:34" s="9" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="12" t="s">
+      <c r="R1" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="12" t="s">
+      <c r="AD1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF1" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="O1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="P1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="R1" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="S1" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="T1" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="V1" s="12" t="s">
+      <c r="AG1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH1" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="W1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="X1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y1" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z1" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA1" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB1" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC1" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD1" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE1" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF1" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH1" s="14" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.35">
@@ -794,10 +794,10 @@
         <v>20.5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="11">
         <v>1</v>
@@ -891,10 +891,10 @@
         <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="11">
         <v>1</v>
@@ -984,13 +984,13 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="11">
         <v>1</v>
@@ -1074,10 +1074,10 @@
         <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="11">
         <v>1</v>
@@ -1155,13 +1155,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="11">
         <v>1</v>
@@ -1247,13 +1247,13 @@
         <v>20.5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="11">
         <v>1</v>
@@ -1351,10 +1351,10 @@
         <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>17</v>
       </c>
       <c r="E8" s="11">
         <v>0</v>
@@ -1436,13 +1436,13 @@
         <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="11">
         <v>1</v>
@@ -1526,10 +1526,10 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" s="11">
         <v>0</v>
@@ -1611,13 +1611,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="11">
         <v>0</v>
@@ -1701,10 +1701,10 @@
         <v>20.5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" s="11">
         <v>0</v>
@@ -1782,13 +1782,13 @@
         <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="11">
         <v>1</v>
@@ -1866,10 +1866,10 @@
         <v>17</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" s="11">
         <v>0</v>
@@ -1953,10 +1953,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" s="11">
         <v>0</v>
@@ -2032,10 +2032,10 @@
         <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E16" s="11">
         <v>0</v>
@@ -2119,13 +2119,13 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" s="11">
         <v>1</v>
@@ -2197,13 +2197,13 @@
         <v>15.5</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="11">
         <v>0</v>
@@ -2283,13 +2283,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19" s="11">
         <v>0</v>
@@ -2367,13 +2367,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" s="11">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>12</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" s="11">
         <v>0.5</v>
@@ -2534,13 +2534,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
         <v>32</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>33</v>
       </c>
       <c r="E22" s="11">
         <v>1</v>
@@ -2638,13 +2638,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="11">
         <v>1</v>
@@ -2736,13 +2736,13 @@
         <v>19</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" s="11">
         <v>1</v>
@@ -2822,10 +2822,10 @@
         <v>20</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" s="11">
         <v>1</v>
@@ -2907,10 +2907,10 @@
         <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" s="11">
         <v>0</v>
@@ -3000,13 +3000,13 @@
         <v>19.5</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" s="11">
         <v>1</v>
